--- a/data/MATRİX.xlsx
+++ b/data/MATRİX.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cerendereli/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cerendereli/needleman_wunsch/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B86111AE-BFB4-9F46-A617-AA93808CE4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6F92C5-6DF6-DA41-A3A6-74716023A140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3880" yWindow="500" windowWidth="24620" windowHeight="16840" xr2:uid="{92AB6EA4-1FD9-6F42-BB78-8D61B221258D}"/>
+    <workbookView xWindow="4020" yWindow="500" windowWidth="24620" windowHeight="16840" activeTab="1" xr2:uid="{92AB6EA4-1FD9-6F42-BB78-8D61B221258D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="21">
   <si>
     <t xml:space="preserve">seq1 </t>
   </si>
@@ -161,7 +162,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,6 +172,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -252,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -264,14 +271,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -286,20 +302,14 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -665,13 +675,13 @@
       <c r="P4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="Q4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="T4" s="2"/>
@@ -679,7 +689,7 @@
       <c r="V4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="W4" s="16" t="s">
+      <c r="W4" s="8" t="s">
         <v>15</v>
       </c>
       <c r="X4" s="3">
@@ -707,7 +717,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="3"/>
-      <c r="W5" s="16"/>
+      <c r="W5" s="8"/>
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="3:27" ht="26" customHeight="1" x14ac:dyDescent="0.25">
@@ -765,7 +775,7 @@
       <c r="V6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W6" s="16" t="s">
+      <c r="W6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="X6" s="3">
@@ -793,7 +803,7 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="3"/>
-      <c r="W7" s="17"/>
+      <c r="W7" s="9"/>
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="3:27" ht="26" customHeight="1" x14ac:dyDescent="0.25">
@@ -819,7 +829,7 @@
       <c r="V8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W8" s="16" t="s">
+      <c r="W8" s="8" t="s">
         <v>11</v>
       </c>
       <c r="X8" s="3">
@@ -847,7 +857,7 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="16"/>
+      <c r="W9" s="8"/>
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="3:27" ht="26" customHeight="1" x14ac:dyDescent="0.25">
@@ -897,7 +907,7 @@
       <c r="V10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W10" s="16" t="s">
+      <c r="W10" s="8" t="s">
         <v>12</v>
       </c>
       <c r="X10" s="3">
@@ -1157,21 +1167,21 @@
         <v>-4</v>
       </c>
       <c r="R15" s="2"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="14" t="s">
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="V15" s="8" t="s">
+      <c r="V15" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="W15" s="9"/>
-      <c r="X15" s="10" t="s">
+      <c r="W15" s="12"/>
+      <c r="X15" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="12"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="15"/>
     </row>
     <row r="16" spans="3:27" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
@@ -1220,19 +1230,19 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="14" t="s">
+      <c r="U16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="V16" s="13" t="s">
+      <c r="V16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="W16" s="9"/>
-      <c r="X16" s="10" t="s">
+      <c r="W16" s="12"/>
+      <c r="X16" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="12"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="15"/>
     </row>
     <row r="17" spans="3:27" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="2"/>
@@ -1281,19 +1291,19 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="15" t="s">
+      <c r="U17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="V17" s="13" t="s">
+      <c r="V17" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="W17" s="9"/>
-      <c r="X17" s="10" t="s">
+      <c r="W17" s="12"/>
+      <c r="X17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="12"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="15"/>
     </row>
     <row r="18" spans="3:27" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="2"/>
@@ -1648,7 +1658,7 @@
       <c r="P24" s="1">
         <v>50</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="Q24" s="5">
         <v>57</v>
       </c>
       <c r="R24" s="2"/>
@@ -1700,7 +1710,7 @@
       <c r="P25" s="1">
         <v>48</v>
       </c>
-      <c r="Q25" s="5">
+      <c r="Q25" s="1">
         <v>55</v>
       </c>
       <c r="R25" s="2"/>
@@ -1774,4 +1784,537 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA154871-1B8C-6141-8B59-4BECCC2D8025}">
+  <dimension ref="A2:W16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.83203125" defaultRowHeight="29" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+    </row>
+    <row r="3" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+    </row>
+    <row r="4" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18">
+        <v>-3</v>
+      </c>
+      <c r="F4" s="18">
+        <v>-6</v>
+      </c>
+      <c r="G4" s="18">
+        <v>-9</v>
+      </c>
+      <c r="H4" s="18">
+        <v>-12</v>
+      </c>
+      <c r="I4" s="18">
+        <v>-15</v>
+      </c>
+      <c r="J4" s="18">
+        <v>-18</v>
+      </c>
+      <c r="K4" s="18">
+        <v>-21</v>
+      </c>
+      <c r="L4" s="18">
+        <v>-24</v>
+      </c>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+    </row>
+    <row r="5" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="18">
+        <v>-2</v>
+      </c>
+      <c r="E5" s="19">
+        <v>5</v>
+      </c>
+      <c r="F5" s="18">
+        <v>2</v>
+      </c>
+      <c r="G5" s="18">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="18">
+        <v>-4</v>
+      </c>
+      <c r="I5" s="18">
+        <v>-7</v>
+      </c>
+      <c r="J5" s="18">
+        <v>-10</v>
+      </c>
+      <c r="K5" s="18">
+        <v>-13</v>
+      </c>
+      <c r="L5" s="18">
+        <v>-16</v>
+      </c>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+    </row>
+    <row r="6" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="18">
+        <v>-4</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3</v>
+      </c>
+      <c r="F6" s="19">
+        <v>10</v>
+      </c>
+      <c r="G6" s="18">
+        <v>7</v>
+      </c>
+      <c r="H6" s="18">
+        <v>4</v>
+      </c>
+      <c r="I6" s="18">
+        <v>1</v>
+      </c>
+      <c r="J6" s="18">
+        <v>-2</v>
+      </c>
+      <c r="K6" s="18">
+        <v>-5</v>
+      </c>
+      <c r="L6" s="18">
+        <v>-8</v>
+      </c>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+    </row>
+    <row r="7" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="18">
+        <v>-6</v>
+      </c>
+      <c r="E7" s="18">
+        <v>1</v>
+      </c>
+      <c r="F7" s="18">
+        <v>8</v>
+      </c>
+      <c r="G7" s="19">
+        <v>15</v>
+      </c>
+      <c r="H7" s="18">
+        <v>12</v>
+      </c>
+      <c r="I7" s="18">
+        <v>9</v>
+      </c>
+      <c r="J7" s="18">
+        <v>6</v>
+      </c>
+      <c r="K7" s="18">
+        <v>3</v>
+      </c>
+      <c r="L7" s="18">
+        <v>0</v>
+      </c>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="R7" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="S7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="18">
+        <v>-8</v>
+      </c>
+      <c r="E8" s="18">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="18">
+        <v>6</v>
+      </c>
+      <c r="G8" s="18">
+        <v>13</v>
+      </c>
+      <c r="H8" s="19">
+        <v>20</v>
+      </c>
+      <c r="I8" s="18">
+        <v>17</v>
+      </c>
+      <c r="J8" s="18">
+        <v>14</v>
+      </c>
+      <c r="K8" s="18">
+        <v>11</v>
+      </c>
+      <c r="L8" s="18">
+        <v>8</v>
+      </c>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+    </row>
+    <row r="9" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="18">
+        <v>-10</v>
+      </c>
+      <c r="E9" s="18">
+        <v>-3</v>
+      </c>
+      <c r="F9" s="18">
+        <v>4</v>
+      </c>
+      <c r="G9" s="18">
+        <v>11</v>
+      </c>
+      <c r="H9" s="18">
+        <v>18</v>
+      </c>
+      <c r="I9" s="19">
+        <v>19</v>
+      </c>
+      <c r="J9" s="19">
+        <v>22</v>
+      </c>
+      <c r="K9" s="18">
+        <v>19</v>
+      </c>
+      <c r="L9" s="18">
+        <v>16</v>
+      </c>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="R9" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="18">
+        <v>-12</v>
+      </c>
+      <c r="E10" s="18">
+        <v>-5</v>
+      </c>
+      <c r="F10" s="18">
+        <v>2</v>
+      </c>
+      <c r="G10" s="18">
+        <v>9</v>
+      </c>
+      <c r="H10" s="18">
+        <v>16</v>
+      </c>
+      <c r="I10" s="18">
+        <v>17</v>
+      </c>
+      <c r="J10" s="18">
+        <v>20</v>
+      </c>
+      <c r="K10" s="19">
+        <v>21</v>
+      </c>
+      <c r="L10" s="18">
+        <v>24</v>
+      </c>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+    </row>
+    <row r="11" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18">
+        <v>-14</v>
+      </c>
+      <c r="E11" s="18">
+        <v>-7</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <v>7</v>
+      </c>
+      <c r="H11" s="18">
+        <v>14</v>
+      </c>
+      <c r="I11" s="18">
+        <v>21</v>
+      </c>
+      <c r="J11" s="18">
+        <v>18</v>
+      </c>
+      <c r="K11" s="19">
+        <v>25</v>
+      </c>
+      <c r="L11" s="18">
+        <v>22</v>
+      </c>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="18">
+        <v>-16</v>
+      </c>
+      <c r="E12" s="18">
+        <v>-9</v>
+      </c>
+      <c r="F12" s="18">
+        <v>-2</v>
+      </c>
+      <c r="G12" s="18">
+        <v>5</v>
+      </c>
+      <c r="H12" s="18">
+        <v>12</v>
+      </c>
+      <c r="I12" s="18">
+        <v>19</v>
+      </c>
+      <c r="J12" s="18">
+        <v>20</v>
+      </c>
+      <c r="K12" s="18">
+        <v>23</v>
+      </c>
+      <c r="L12" s="19">
+        <v>30</v>
+      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="13" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+    </row>
+    <row r="14" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+    </row>
+    <row r="15" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+    </row>
+    <row r="16" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>